--- a/data/trans_bre/IP07B_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP07B_R2-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,297 +619,285 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-1,5</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-2,54</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,81</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,54</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-51,99%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-53,99%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-34,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>96,13%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-1.502205389144901</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-2.538952691052817</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.8097485959870485</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.543658838284502</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.5199264015233064</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.5399312565564628</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.3487032623984113</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.9613403871871293</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-4,91; 1,59</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-6,37; 0,84</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-3,72; 1,49</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-1,64; 6,43</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 433,36</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-89,91; 53,1</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-90,91; 201,13</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-4.91032512466422</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-6.368123824939858</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.718598110522099</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-1.639370424001908</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.899134085257861</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.9090991610231045</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.594466593897202</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.8382357334673251</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.486419419222758</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>6.431240021550125</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>4.333551725686283</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.530999127747659</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>2.011303020302295</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>12-15</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,44</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,45</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,54</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,09</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>122,15%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>53,89%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>49,98%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-79,25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,8; 3,77</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-1,57; 4,96</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-1,85; 2,54</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-3,67; 0,07</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-57,24; 944,72</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-43,24; 345,82</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.442403702594167</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.449984104158993</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.536495479198052</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1.087140664485407</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1.221479810901702</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.5388899060263836</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.4998452017406646</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.7925107630720827</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,28</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>15,23%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-12,29%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-8,41%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-8,61%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.8047478703647982</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-1.57177020914091</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.848647056085174</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-3.672055670740838</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5723533381539299</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4323741976335402</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-1,57; 2,44</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-2,83; 1,94</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,87; 1,49</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-2,27; 1,68</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-62,28; 238,28</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-58,81; 83,02</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-71,16; 184,35</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 282,38</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.771947542974642</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.956658497884817</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.538171434608628</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0.06709027292530362</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>9.447186558326733</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>3.45820247327193</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.2839642999543139</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.4479617256320623</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.1431068327300781</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.1253895486138853</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.1522837378403357</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.1228768053861659</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.08412222187683181</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.08607058836357369</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-1.5667290888949</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.8266818738968</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.866977084903392</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.265197276176746</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.6227929288818084</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.5880776911383191</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.7115841398245444</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2.439829687839148</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.937722399442161</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.49285524139396</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1.682598887999257</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>2.382792856701301</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.8302012717837844</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.843535158006919</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>2.823813403698435</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -908,11 +905,11 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A1:B2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
